--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-signe-vital-observe.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-signe-vital-observe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3044" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3393" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,6 +549,9 @@
     <t>Observation.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>Identifiant de l'entrée</t>
   </si>
   <si>
@@ -562,13 +565,136 @@
     <t>Observation.code</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Signe vital observé</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis</t>
+  </si>
+  <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.derivationExpr</t>
@@ -581,10 +707,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Description narrative</t>
   </si>
   <si>
@@ -734,123 +856,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -1375,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK96"/>
+  <dimension ref="A1:AK107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.671875" customWidth="true" bestFit="true"/>
@@ -5312,7 +5345,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>173</v>
       </c>
@@ -5331,7 +5364,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5343,10 +5376,10 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5417,10 +5450,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5443,7 +5476,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
@@ -5496,7 +5529,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5516,10 +5549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5533,7 +5566,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5542,7 +5575,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>179</v>
@@ -5597,7 +5630,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5626,7 +5659,9 @@
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5643,10 +5678,12 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
+      <c r="M42" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5672,13 +5709,11 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -5696,7 +5731,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5716,16 +5751,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F43" t="s" s="2">
         <v>75</v>
       </c>
@@ -5733,7 +5770,7 @@
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5742,13 +5779,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5799,7 +5834,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5817,28 +5852,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -5847,11 +5882,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5878,11 +5913,13 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>74</v>
@@ -5900,7 +5937,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>89</v>
+        <v>188</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5920,17 +5957,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5948,11 +5985,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5979,11 +6016,13 @@
         <v>74</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>190</v>
+        <v>74</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>74</v>
@@ -6001,7 +6040,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6021,17 +6060,17 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>80</v>
@@ -6049,7 +6088,7 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>194</v>
+        <v>102</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
@@ -6122,7 +6161,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>197</v>
       </c>
@@ -6143,7 +6182,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6152,7 +6191,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
@@ -6183,29 +6222,31 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6225,18 +6266,16 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
@@ -6253,11 +6292,11 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6308,7 +6347,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6328,18 +6367,16 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>207</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
@@ -6356,11 +6393,11 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6387,11 +6424,13 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6409,7 +6448,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6429,16 +6468,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" s="2"/>
+      <c r="E50" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
@@ -6455,10 +6496,12 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
+      <c r="M50" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6484,11 +6527,13 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>213</v>
+        <v>74</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6506,7 +6551,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6526,21 +6571,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6552,17 +6599,13 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L51" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L51" s="2"/>
+      <c r="M51" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M51" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>218</v>
-      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>74</v>
@@ -6611,13 +6654,13 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
@@ -6629,28 +6672,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>74</v>
@@ -6659,11 +6702,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6714,13 +6757,13 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>74</v>
@@ -6734,18 +6777,16 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
@@ -6762,12 +6803,10 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="L53" s="2"/>
-      <c r="M53" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6817,7 +6856,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6837,10 +6876,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6854,7 +6893,7 @@
         <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>74</v>
@@ -6863,13 +6902,13 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6896,11 +6935,13 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>231</v>
+        <v>74</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6918,7 +6959,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6938,10 +6979,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7039,17 +7080,17 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>62</v>
+        <v>228</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
@@ -7071,7 +7112,7 @@
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7083,7 +7124,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>235</v>
+        <v>74</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7098,13 +7139,11 @@
         <v>74</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>74</v>
+        <v>230</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7122,7 +7161,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7142,23 +7181,23 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>74</v>
@@ -7170,11 +7209,11 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7225,7 +7264,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7245,23 +7284,23 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7273,11 +7312,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7304,13 +7343,11 @@
         <v>74</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>74</v>
+        <v>240</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7328,7 +7365,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7348,23 +7385,23 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>74</v>
@@ -7376,11 +7413,11 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7431,7 +7468,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7451,23 +7488,23 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>74</v>
@@ -7479,11 +7516,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7510,13 +7547,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>250</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7534,7 +7569,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7554,10 +7589,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7580,12 +7615,10 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>254</v>
+        <v>85</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" t="s" s="2">
-        <v>255</v>
-      </c>
+      <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7611,13 +7644,11 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -7635,7 +7666,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7655,10 +7686,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7683,11 +7714,15 @@
       <c r="K62" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L62" s="2"/>
+      <c r="L62" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="M62" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>74</v>
@@ -7754,7 +7789,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>260</v>
       </c>
@@ -7769,13 +7804,13 @@
         <v>261</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>74</v>
@@ -7784,11 +7819,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7839,7 +7874,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7859,23 +7894,23 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>74</v>
@@ -7887,7 +7922,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
@@ -7948,7 +7983,7 @@
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -7960,7 +7995,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>269</v>
       </c>
@@ -7971,30 +8006,30 @@
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E65" t="s" s="2">
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8021,13 +8056,11 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>74</v>
+        <v>271</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8045,44 +8078,46 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="AG65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="B66" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F66" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>74</v>
@@ -8091,13 +8126,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>276</v>
+        <v>86</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8124,13 +8157,11 @@
         <v>74</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>74</v>
@@ -8148,7 +8179,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>273</v>
+        <v>89</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8168,16 +8199,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -8194,10 +8227,12 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>278</v>
+        <v>85</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+      <c r="M67" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8208,7 +8243,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8223,11 +8258,13 @@
         <v>74</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>279</v>
+        <v>74</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>74</v>
@@ -8245,7 +8282,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>277</v>
+        <v>184</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8265,21 +8302,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8291,10 +8330,12 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>281</v>
+        <v>112</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
+      <c r="M68" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8344,7 +8385,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8364,21 +8405,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8390,10 +8433,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8419,11 +8464,13 @@
         <v>74</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y69" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z69" t="s" s="2">
-        <v>283</v>
+        <v>74</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>74</v>
@@ -8441,7 +8488,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8459,26 +8506,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="F70" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>74</v>
@@ -8487,13 +8536,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>287</v>
+        <v>195</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8544,13 +8591,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8562,26 +8609,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8590,13 +8639,11 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>289</v>
+        <v>199</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8623,11 +8670,13 @@
         <v>74</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>290</v>
+        <v>74</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>74</v>
@@ -8645,13 +8694,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8663,12 +8712,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8682,7 +8731,7 @@
         <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>74</v>
@@ -8691,13 +8740,11 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8724,11 +8771,13 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>293</v>
+        <v>74</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -8746,13 +8795,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8766,10 +8815,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8792,13 +8841,11 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8849,13 +8896,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>294</v>
+        <v>207</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8869,21 +8916,23 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -8895,10 +8944,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>297</v>
+        <v>210</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8948,7 +8999,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>296</v>
+        <v>212</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8968,21 +9019,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -8994,10 +9047,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>299</v>
+        <v>215</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9047,7 +9102,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>298</v>
+        <v>217</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9067,21 +9122,23 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>74</v>
@@ -9093,10 +9150,12 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>301</v>
+        <v>177</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9146,7 +9205,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>300</v>
+        <v>221</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9164,12 +9223,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9177,13 +9236,13 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>74</v>
@@ -9192,13 +9251,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9249,13 +9308,13 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>74</v>
@@ -9269,10 +9328,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9283,7 +9342,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>74</v>
@@ -9295,7 +9354,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9324,13 +9383,11 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9348,13 +9405,13 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>74</v>
@@ -9368,10 +9425,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9382,7 +9439,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>74</v>
@@ -9394,7 +9451,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -9447,13 +9504,13 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>74</v>
@@ -9467,10 +9524,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9481,7 +9538,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9493,7 +9550,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>310</v>
+        <v>91</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9522,13 +9579,11 @@
         <v>74</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>74</v>
+        <v>294</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>74</v>
@@ -9546,13 +9601,13 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
@@ -9564,12 +9619,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9577,13 +9632,13 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>74</v>
@@ -9592,10 +9647,14 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9645,7 +9704,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9663,12 +9722,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9679,10 +9738,10 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>74</v>
@@ -9691,10 +9750,14 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9720,13 +9783,11 @@
         <v>74</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>74</v>
+        <v>301</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -9744,7 +9805,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9762,12 +9823,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9778,10 +9839,10 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>74</v>
@@ -9790,10 +9851,14 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9819,13 +9884,11 @@
         <v>74</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>74</v>
+        <v>304</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>74</v>
@@ -9843,7 +9906,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9863,10 +9926,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9877,7 +9940,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9889,11 +9952,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="L84" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="M84" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9944,7 +10009,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9964,18 +10029,16 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E85" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
@@ -9992,12 +10055,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>85</v>
+        <v>308</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10023,11 +10084,13 @@
         <v>74</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10045,7 +10108,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>89</v>
+        <v>307</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10065,10 +10128,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10091,12 +10154,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>91</v>
+        <v>310</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10146,7 +10207,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>93</v>
+        <v>309</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10166,10 +10227,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10180,7 +10241,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10192,12 +10253,10 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>95</v>
+        <v>312</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M87" s="2"/>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10247,19 +10306,19 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>97</v>
+        <v>311</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>74</v>
@@ -10267,18 +10326,16 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
@@ -10295,11 +10352,13 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L88" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="M88" t="s" s="2">
-        <v>86</v>
+        <v>315</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10326,11 +10385,13 @@
         <v>74</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10348,13 +10409,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>89</v>
+        <v>313</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10368,23 +10429,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10396,12 +10455,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>102</v>
+        <v>317</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10451,13 +10508,13 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>74</v>
@@ -10471,23 +10528,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>74</v>
@@ -10499,12 +10554,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>319</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10554,13 +10607,13 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>109</v>
+        <v>318</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>74</v>
@@ -10574,23 +10627,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>74</v>
@@ -10602,12 +10653,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>112</v>
+        <v>321</v>
       </c>
       <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M91" s="2"/>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -10615,7 +10664,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>74</v>
@@ -10657,13 +10706,13 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>115</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>74</v>
@@ -10677,23 +10726,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -10705,12 +10752,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>102</v>
+        <v>323</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10760,13 +10805,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>119</v>
+        <v>322</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -10780,10 +10825,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10806,12 +10851,10 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -10861,7 +10904,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>125</v>
+        <v>324</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10881,10 +10924,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10895,7 +10938,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -10907,7 +10950,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>85</v>
+        <v>327</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10918,7 +10961,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>330</v>
+        <v>74</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>74</v>
@@ -10936,11 +10979,13 @@
         <v>74</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>331</v>
+        <v>74</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>74</v>
@@ -10958,13 +11003,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -10978,10 +11023,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10989,10 +11034,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>74</v>
@@ -11004,10 +11049,12 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
+      <c r="M95" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11057,13 +11104,13 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>74</v>
@@ -11077,21 +11124,23 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>74</v>
@@ -11103,10 +11152,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>335</v>
+        <v>85</v>
       </c>
       <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11132,13 +11183,11 @@
         <v>74</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>74</v>
@@ -11156,26 +11205,1137 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
+      <c r="B99" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y99" s="2"/>
+      <c r="Z99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK96" t="s" s="2">
+      <c r="H104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L104" s="2"/>
+      <c r="M104" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y105" s="2"/>
+      <c r="Z105" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK107" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK96">
+  <autoFilter ref="A1:AK107">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11185,7 +12345,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
